--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/72.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/72.xlsx
@@ -426,13 +426,13 @@
         <v>-4.35739033045159</v>
       </c>
       <c r="E2">
-        <v>-14.74032535436885</v>
+        <v>-21.49189065104069</v>
       </c>
       <c r="F2">
-        <v>-4.711421218871267</v>
+        <v>-5.507378350470852</v>
       </c>
       <c r="G2">
-        <v>-6.250585904092095</v>
+        <v>-7.873935083092496</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.63854822371253</v>
       </c>
       <c r="E3">
-        <v>-15.78153926905647</v>
+        <v>-24.33697690194372</v>
       </c>
       <c r="F3">
-        <v>-4.982449522562954</v>
+        <v>-4.721242571105864</v>
       </c>
       <c r="G3">
-        <v>-4.984596873873861</v>
+        <v>-8.235625425440031</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.052746445631192</v>
       </c>
       <c r="E4">
-        <v>-16.02415226401741</v>
+        <v>-23.44672872524981</v>
       </c>
       <c r="F4">
-        <v>-4.726245498092737</v>
+        <v>-5.123821406663529</v>
       </c>
       <c r="G4">
-        <v>-5.09098125477834</v>
+        <v>-9.322927760176102</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.683697570328197</v>
       </c>
       <c r="E5">
-        <v>-16.85999535398316</v>
+        <v>-21.60968531692822</v>
       </c>
       <c r="F5">
-        <v>-4.62858072984646</v>
+        <v>-4.744100198583402</v>
       </c>
       <c r="G5">
-        <v>-5.730174766409743</v>
+        <v>-7.991091979181764</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.505958979131402</v>
       </c>
       <c r="E6">
-        <v>-17.423129210733</v>
+        <v>-23.2082638124799</v>
       </c>
       <c r="F6">
-        <v>-3.743262991968204</v>
+        <v>-4.44086802695421</v>
       </c>
       <c r="G6">
-        <v>-5.362783664643583</v>
+        <v>-7.961088504959349</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.52151201507691</v>
       </c>
       <c r="E7">
-        <v>-18.45633678337506</v>
+        <v>-22.89793201720826</v>
       </c>
       <c r="F7">
-        <v>-4.244873333977171</v>
+        <v>-4.850784963871065</v>
       </c>
       <c r="G7">
-        <v>-6.000924422793497</v>
+        <v>-11.28160209684928</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.703605482565687</v>
       </c>
       <c r="E8">
-        <v>-18.30316567853961</v>
+        <v>-24.42928984459008</v>
       </c>
       <c r="F8">
-        <v>-4.154723250299654</v>
+        <v>-4.56633396069307</v>
       </c>
       <c r="G8">
-        <v>-7.07591152812348</v>
+        <v>-9.537461042757492</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.01776059944548</v>
       </c>
       <c r="E9">
-        <v>-19.05263718375707</v>
+        <v>-23.72225919777251</v>
       </c>
       <c r="F9">
-        <v>-3.877378335564236</v>
+        <v>-4.205796974219618</v>
       </c>
       <c r="G9">
-        <v>-6.431139747258406</v>
+        <v>-10.14230764441896</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.417896979268784</v>
       </c>
       <c r="E10">
-        <v>-20.639550330265</v>
+        <v>-27.36062541144319</v>
       </c>
       <c r="F10">
-        <v>-3.88807943643486</v>
+        <v>-4.031155388100449</v>
       </c>
       <c r="G10">
-        <v>-6.783404966455635</v>
+        <v>-10.80364539516254</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.861170163208225</v>
       </c>
       <c r="E11">
-        <v>-18.65091625453664</v>
+        <v>-26.0248795472967</v>
       </c>
       <c r="F11">
-        <v>-3.024452134774463</v>
+        <v>-4.800660671647406</v>
       </c>
       <c r="G11">
-        <v>-7.01804319209702</v>
+        <v>-9.554344825007776</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.295327530882431</v>
       </c>
       <c r="E12">
-        <v>-19.3010285115518</v>
+        <v>-26.34152856380904</v>
       </c>
       <c r="F12">
-        <v>-3.493666188577201</v>
+        <v>-4.804797311498534</v>
       </c>
       <c r="G12">
-        <v>-7.802172387437714</v>
+        <v>-10.3380635127016</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.673013714552126</v>
       </c>
       <c r="E13">
-        <v>-20.16944038658072</v>
+        <v>-25.26069503002832</v>
       </c>
       <c r="F13">
-        <v>-3.169197312474925</v>
+        <v>-4.584986057112158</v>
       </c>
       <c r="G13">
-        <v>-6.307924552832271</v>
+        <v>-11.47621582692088</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.96281184424884</v>
       </c>
       <c r="E14">
-        <v>-19.68759263826857</v>
+        <v>-26.38295957250522</v>
       </c>
       <c r="F14">
-        <v>-3.218257354323408</v>
+        <v>-4.902219772739749</v>
       </c>
       <c r="G14">
-        <v>-7.044537488047807</v>
+        <v>-9.214096886118101</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.139581718994688</v>
       </c>
       <c r="E15">
-        <v>-20.47657960767696</v>
+        <v>-28.69415232332593</v>
       </c>
       <c r="F15">
-        <v>-2.789529950395922</v>
+        <v>-4.689320602821309</v>
       </c>
       <c r="G15">
-        <v>-5.964968587691473</v>
+        <v>-9.913158303281683</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.189050899281225</v>
       </c>
       <c r="E16">
-        <v>-21.25813082276475</v>
+        <v>-26.51258261250078</v>
       </c>
       <c r="F16">
-        <v>-2.750472595109354</v>
+        <v>-4.442537252989084</v>
       </c>
       <c r="G16">
-        <v>-6.083883383462094</v>
+        <v>-9.630642968051358</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.115363638980819</v>
       </c>
       <c r="E17">
-        <v>-22.15115948249937</v>
+        <v>-27.59881408729864</v>
       </c>
       <c r="F17">
-        <v>-2.530276500185527</v>
+        <v>-3.460663341005358</v>
       </c>
       <c r="G17">
-        <v>-7.417513480138717</v>
+        <v>-7.428292616414584</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.930470995837714</v>
       </c>
       <c r="E18">
-        <v>-23.45838501734556</v>
+        <v>-30.0387400329724</v>
       </c>
       <c r="F18">
-        <v>-2.544101460974355</v>
+        <v>-3.867667842743719</v>
       </c>
       <c r="G18">
-        <v>-5.695920551714903</v>
+        <v>-8.395316210617855</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.651356444528615</v>
       </c>
       <c r="E19">
-        <v>-23.7123373112217</v>
+        <v>-29.92853508952174</v>
       </c>
       <c r="F19">
-        <v>-1.71547406004517</v>
+        <v>-4.463292510863876</v>
       </c>
       <c r="G19">
-        <v>-5.760741033373834</v>
+        <v>-6.596359143486813</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.303415049258831</v>
       </c>
       <c r="E20">
-        <v>-22.48827720152638</v>
+        <v>-30.02009856971983</v>
       </c>
       <c r="F20">
-        <v>-2.079115110112883</v>
+        <v>-4.051586778115532</v>
       </c>
       <c r="G20">
-        <v>-5.322947870169533</v>
+        <v>-8.174522686421701</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.913842549603216</v>
       </c>
       <c r="E21">
-        <v>-24.84615851936618</v>
+        <v>-34.26702149867429</v>
       </c>
       <c r="F21">
-        <v>-1.829099416507246</v>
+        <v>-3.844021529720293</v>
       </c>
       <c r="G21">
-        <v>-4.739189443593227</v>
+        <v>-8.364634074559889</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.506046591281263</v>
       </c>
       <c r="E22">
-        <v>-24.58951178345547</v>
+        <v>-30.11374967643545</v>
       </c>
       <c r="F22">
-        <v>-1.531684988558422</v>
+        <v>-3.143773289561417</v>
       </c>
       <c r="G22">
-        <v>-5.475898384629401</v>
+        <v>-6.959631926602118</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.101646288458102</v>
       </c>
       <c r="E23">
-        <v>-24.26237029266735</v>
+        <v>-32.60891847652879</v>
       </c>
       <c r="F23">
-        <v>-1.062910413147218</v>
+        <v>-3.998658534568589</v>
       </c>
       <c r="G23">
-        <v>-4.454237546845999</v>
+        <v>-7.303892246685391</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.721884269413771</v>
       </c>
       <c r="E24">
-        <v>-25.4562798224196</v>
+        <v>-31.66208022439803</v>
       </c>
       <c r="F24">
-        <v>-1.137491083970051</v>
+        <v>-3.557264650729418</v>
       </c>
       <c r="G24">
-        <v>-5.374522859125839</v>
+        <v>-7.010932140278666</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.379211088704526</v>
       </c>
       <c r="E25">
-        <v>-25.99441197417309</v>
+        <v>-30.36623248049611</v>
       </c>
       <c r="F25">
-        <v>-1.537189950320489</v>
+        <v>-2.73797953099541</v>
       </c>
       <c r="G25">
-        <v>-5.73141291044143</v>
+        <v>-8.304809206119719</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.078833078291134</v>
       </c>
       <c r="E26">
-        <v>-26.36754464698311</v>
+        <v>-33.72250872704399</v>
       </c>
       <c r="F26">
-        <v>-1.120481290585273</v>
+        <v>-3.69585950650727</v>
       </c>
       <c r="G26">
-        <v>-5.174433486732289</v>
+        <v>-8.648218715999398</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.828539049062612</v>
       </c>
       <c r="E27">
-        <v>-26.7020539649817</v>
+        <v>-33.37724428327719</v>
       </c>
       <c r="F27">
-        <v>-1.626968654960836</v>
+        <v>-2.351861734722822</v>
       </c>
       <c r="G27">
-        <v>-5.3052000355335</v>
+        <v>-8.013143523018849</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.626156643297074</v>
       </c>
       <c r="E28">
-        <v>-25.29138902685231</v>
+        <v>-32.19291247605116</v>
       </c>
       <c r="F28">
-        <v>-0.4619462805331577</v>
+        <v>-3.708383452886566</v>
       </c>
       <c r="G28">
-        <v>-5.663384510154946</v>
+        <v>-7.85461142877977</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.463334757850308</v>
       </c>
       <c r="E29">
-        <v>-25.85855322546898</v>
+        <v>-32.97757248854521</v>
       </c>
       <c r="F29">
-        <v>-1.298759065486292</v>
+        <v>-2.757836827616147</v>
       </c>
       <c r="G29">
-        <v>-5.023499094505836</v>
+        <v>-7.495612559955664</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.334379826014447</v>
       </c>
       <c r="E30">
-        <v>-26.93327784781335</v>
+        <v>-29.67151249026839</v>
       </c>
       <c r="F30">
-        <v>-0.6822271037234614</v>
+        <v>-2.976030326409902</v>
       </c>
       <c r="G30">
-        <v>-5.095122747247968</v>
+        <v>-8.014477672871175</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.229166872023892</v>
       </c>
       <c r="E31">
-        <v>-26.81199172846592</v>
+        <v>-33.32393282302188</v>
       </c>
       <c r="F31">
-        <v>-0.8261780529073299</v>
+        <v>-2.867180635135833</v>
       </c>
       <c r="G31">
-        <v>-5.908911120074994</v>
+        <v>-8.239058461164255</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.135306674499874</v>
       </c>
       <c r="E32">
-        <v>-26.23471091891611</v>
+        <v>-33.0522447606947</v>
       </c>
       <c r="F32">
-        <v>-0.628746146812029</v>
+        <v>-2.662075673880228</v>
       </c>
       <c r="G32">
-        <v>-4.778806742061685</v>
+        <v>-5.654177883010233</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.043506876414093</v>
       </c>
       <c r="E33">
-        <v>-27.3510069326509</v>
+        <v>-33.0821236321973</v>
       </c>
       <c r="F33">
-        <v>-1.316965348690184</v>
+        <v>-3.5677305712716</v>
       </c>
       <c r="G33">
-        <v>-4.731005775020148</v>
+        <v>-7.886343007773684</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9460651845417432</v>
       </c>
       <c r="E34">
-        <v>-27.08014984530412</v>
+        <v>-31.89624761533466</v>
       </c>
       <c r="F34">
-        <v>-0.8269889103360349</v>
+        <v>-2.805924474032551</v>
       </c>
       <c r="G34">
-        <v>-5.898625255084478</v>
+        <v>-7.932415870043721</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.8355019137586962</v>
       </c>
       <c r="E35">
-        <v>-26.60402608813766</v>
+        <v>-32.14326002279405</v>
       </c>
       <c r="F35">
-        <v>-0.6365593599458494</v>
+        <v>-3.031032432853114</v>
       </c>
       <c r="G35">
-        <v>-5.857796296948647</v>
+        <v>-6.503140802192015</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.7070193998392852</v>
       </c>
       <c r="E36">
-        <v>-26.36542079267351</v>
+        <v>-32.92339382551745</v>
       </c>
       <c r="F36">
-        <v>-1.130151398904947</v>
+        <v>-3.025361181969925</v>
       </c>
       <c r="G36">
-        <v>-5.225591346950646</v>
+        <v>-7.173049555336775</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5594484142809092</v>
       </c>
       <c r="E37">
-        <v>-25.0399953207905</v>
+        <v>-34.04105064569154</v>
       </c>
       <c r="F37">
-        <v>-1.187794334962154</v>
+        <v>-2.825269441789644</v>
       </c>
       <c r="G37">
-        <v>-5.21180954587066</v>
+        <v>-9.565805933664732</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.3925633127023315</v>
       </c>
       <c r="E38">
-        <v>-26.4493651153537</v>
+        <v>-31.47033784220225</v>
       </c>
       <c r="F38">
-        <v>-0.8751256516358169</v>
+        <v>-2.851330114481157</v>
       </c>
       <c r="G38">
-        <v>-5.029428281566671</v>
+        <v>-7.087783144427307</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.2082153907542367</v>
       </c>
       <c r="E39">
-        <v>-26.67386874275796</v>
+        <v>-32.84625127079678</v>
       </c>
       <c r="F39">
-        <v>-0.8046166887215795</v>
+        <v>-2.948638548896461</v>
       </c>
       <c r="G39">
-        <v>-5.192836809385097</v>
+        <v>-7.153523957746153</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.01076592524057694</v>
       </c>
       <c r="E40">
-        <v>-25.81536969733183</v>
+        <v>-31.96291354543858</v>
       </c>
       <c r="F40">
-        <v>-0.5879649276365054</v>
+        <v>-2.62952972546499</v>
       </c>
       <c r="G40">
-        <v>-5.223237549072224</v>
+        <v>-6.41640450906311</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.1950376028188356</v>
       </c>
       <c r="E41">
-        <v>-26.82262005696192</v>
+        <v>-31.07365484031535</v>
       </c>
       <c r="F41">
-        <v>-1.100092660629906</v>
+        <v>-2.617746161601163</v>
       </c>
       <c r="G41">
-        <v>-4.78114729775795</v>
+        <v>-6.42812052972659</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.4032290236232987</v>
       </c>
       <c r="E42">
-        <v>-25.9556255942974</v>
+        <v>-33.40237957825676</v>
       </c>
       <c r="F42">
-        <v>-0.630746367383229</v>
+        <v>-2.585992857996602</v>
       </c>
       <c r="G42">
-        <v>-5.476053980269747</v>
+        <v>-6.404397160392173</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.6085388117728452</v>
       </c>
       <c r="E43">
-        <v>-23.92826853732945</v>
+        <v>-31.57750417959377</v>
       </c>
       <c r="F43">
-        <v>-0.6959942592463765</v>
+        <v>-2.876807191542832</v>
       </c>
       <c r="G43">
-        <v>-4.592174737285272</v>
+        <v>-4.900558675359462</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.8058980687805234</v>
       </c>
       <c r="E44">
-        <v>-24.76078772737358</v>
+        <v>-33.04227758940382</v>
       </c>
       <c r="F44">
-        <v>-1.131016102334776</v>
+        <v>-1.82124661072554</v>
       </c>
       <c r="G44">
-        <v>-4.417563323361953</v>
+        <v>-4.659925051746457</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.9897217127655803</v>
       </c>
       <c r="E45">
-        <v>-25.63570701955152</v>
+        <v>-32.24871912548468</v>
       </c>
       <c r="F45">
-        <v>-0.388909722977879</v>
+        <v>-1.949389007461491</v>
       </c>
       <c r="G45">
-        <v>-3.455621416561463</v>
+        <v>-5.450539605798584</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.156382753546232</v>
       </c>
       <c r="E46">
-        <v>-25.06497891189082</v>
+        <v>-34.00649159630201</v>
       </c>
       <c r="F46">
-        <v>-0.9788077105078067</v>
+        <v>-1.847797440397882</v>
       </c>
       <c r="G46">
-        <v>-4.477725867447128</v>
+        <v>-5.918703713780158</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.30312088175479</v>
       </c>
       <c r="E47">
-        <v>-23.69225805747169</v>
+        <v>-32.24539522556305</v>
       </c>
       <c r="F47">
-        <v>-0.8466506192762157</v>
+        <v>-2.172326497324945</v>
       </c>
       <c r="G47">
-        <v>-3.832156245107089</v>
+        <v>-4.985494031715003</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.427730930518512</v>
       </c>
       <c r="E48">
-        <v>-24.50376059964622</v>
+        <v>-29.01710950413096</v>
       </c>
       <c r="F48">
-        <v>-0.5379736667097439</v>
+        <v>-1.939520144049431</v>
       </c>
       <c r="G48">
-        <v>-3.722381865570396</v>
+        <v>-7.636926506844993</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.529686591424298</v>
       </c>
       <c r="E49">
-        <v>-26.30848428897507</v>
+        <v>-28.73606335026692</v>
       </c>
       <c r="F49">
-        <v>-0.5040712741779316</v>
+        <v>-2.637930493493438</v>
       </c>
       <c r="G49">
-        <v>-4.093983981262508</v>
+        <v>-7.189509587758032</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.609982647527125</v>
       </c>
       <c r="E50">
-        <v>-23.81521065525395</v>
+        <v>-29.38925044113329</v>
       </c>
       <c r="F50">
-        <v>-1.177482825746728</v>
+        <v>-2.111220788283629</v>
       </c>
       <c r="G50">
-        <v>-3.415457878079025</v>
+        <v>-7.770646062267235</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.66989385465206</v>
       </c>
       <c r="E51">
-        <v>-23.43947863836353</v>
+        <v>-31.12924865147051</v>
       </c>
       <c r="F51">
-        <v>-0.4671416277887568</v>
+        <v>-2.329498223490902</v>
       </c>
       <c r="G51">
-        <v>-3.537335612107293</v>
+        <v>-6.738586800944982</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.710556127694382</v>
       </c>
       <c r="E52">
-        <v>-23.14027330372874</v>
+        <v>-31.19976831295496</v>
       </c>
       <c r="F52">
-        <v>-0.5268734719484288</v>
+        <v>-2.042742928205943</v>
       </c>
       <c r="G52">
-        <v>-3.751776199413585</v>
+        <v>-6.019278087263217</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.735225554208101</v>
       </c>
       <c r="E53">
-        <v>-22.88322353363134</v>
+        <v>-30.50186933397385</v>
       </c>
       <c r="F53">
-        <v>-0.5654351272834639</v>
+        <v>-2.113238429619899</v>
       </c>
       <c r="G53">
-        <v>-2.805522967923701</v>
+        <v>-6.333296573845246</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.746095647929713</v>
       </c>
       <c r="E54">
-        <v>-22.82306728491345</v>
+        <v>-29.90249862821464</v>
       </c>
       <c r="F54">
-        <v>-1.456892101142921</v>
+        <v>-1.360591695542794</v>
       </c>
       <c r="G54">
-        <v>-2.542857663746847</v>
+        <v>-6.069479199820725</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.743351001942146</v>
       </c>
       <c r="E55">
-        <v>-23.11552519327682</v>
+        <v>-29.21958210548791</v>
       </c>
       <c r="F55">
-        <v>-0.8365727066833167</v>
+        <v>-2.742172392406536</v>
       </c>
       <c r="G55">
-        <v>-3.803821285836467</v>
+        <v>-6.802632614947722</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.729311215241018</v>
       </c>
       <c r="E56">
-        <v>-22.35625859878077</v>
+        <v>-29.68236497822777</v>
       </c>
       <c r="F56">
-        <v>-0.4687506729988433</v>
+        <v>-2.107417518527702</v>
       </c>
       <c r="G56">
-        <v>-4.610392669387881</v>
+        <v>-6.035105805486472</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.705543942369529</v>
       </c>
       <c r="E57">
-        <v>-22.21096703871867</v>
+        <v>-26.6714143098458</v>
       </c>
       <c r="F57">
-        <v>-1.520306853408947</v>
+        <v>-2.216145264446281</v>
       </c>
       <c r="G57">
-        <v>-4.591853614367962</v>
+        <v>-5.944251193706714</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.671930870213304</v>
       </c>
       <c r="E58">
-        <v>-20.60214966343565</v>
+        <v>-28.22334499464447</v>
       </c>
       <c r="F58">
-        <v>-0.89445319862784</v>
+        <v>-2.54500258964024</v>
       </c>
       <c r="G58">
-        <v>-4.128754641061473</v>
+        <v>-7.631387964157793</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.63030234679074</v>
       </c>
       <c r="E59">
-        <v>-20.37921741651204</v>
+        <v>-27.47348404066236</v>
       </c>
       <c r="F59">
-        <v>-0.111963902133152</v>
+        <v>-1.596752337947209</v>
       </c>
       <c r="G59">
-        <v>-3.59163186949688</v>
+        <v>-7.733889075144707</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.583413321726417</v>
       </c>
       <c r="E60">
-        <v>-21.889400099434</v>
+        <v>-27.78557741232298</v>
       </c>
       <c r="F60">
-        <v>-1.360670088985608</v>
+        <v>-2.477528799112942</v>
       </c>
       <c r="G60">
-        <v>-5.144075784137171</v>
+        <v>-7.629875044846345</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.5325069423809</v>
       </c>
       <c r="E61">
-        <v>-21.54633196556091</v>
+        <v>-27.52237797452317</v>
       </c>
       <c r="F61">
-        <v>-1.055336339606629</v>
+        <v>-2.456024448340148</v>
       </c>
       <c r="G61">
-        <v>-3.993714177969062</v>
+        <v>-5.764885836389001</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.479905531451035</v>
       </c>
       <c r="E62">
-        <v>-22.21470755824901</v>
+        <v>-27.6311428632394</v>
       </c>
       <c r="F62">
-        <v>-1.634124630139749</v>
+        <v>-1.915523832018692</v>
       </c>
       <c r="G62">
-        <v>-4.582431801763197</v>
+        <v>-8.049145705758423</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.431803455047251</v>
       </c>
       <c r="E63">
-        <v>-20.55628980715997</v>
+        <v>-28.43315825236786</v>
       </c>
       <c r="F63">
-        <v>-1.126916679572662</v>
+        <v>-1.57585375468707</v>
       </c>
       <c r="G63">
-        <v>-4.374880459724129</v>
+        <v>-7.921894956319917</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.392917101432196</v>
       </c>
       <c r="E64">
-        <v>-21.48383449578105</v>
+        <v>-27.6512175885154</v>
       </c>
       <c r="F64">
-        <v>-1.41478690382209</v>
+        <v>-2.382821601663748</v>
       </c>
       <c r="G64">
-        <v>-4.162588416472825</v>
+        <v>-7.5971966498282</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.367192309428511</v>
       </c>
       <c r="E65">
-        <v>-20.44107637145682</v>
+        <v>-28.08809306145739</v>
       </c>
       <c r="F65">
-        <v>-1.048691901438403</v>
+        <v>-3.488920613801586</v>
       </c>
       <c r="G65">
-        <v>-5.494702283292462</v>
+        <v>-8.121073928690169</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.363000853282294</v>
       </c>
       <c r="E66">
-        <v>-21.07083766628151</v>
+        <v>-28.03433554651233</v>
       </c>
       <c r="F66">
-        <v>-1.631793415032222</v>
+        <v>-2.032198614220947</v>
       </c>
       <c r="G66">
-        <v>-5.150700185761253</v>
+        <v>-7.227829152375095</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.385621297608476</v>
       </c>
       <c r="E67">
-        <v>-20.99006780388071</v>
+        <v>-26.20721855321555</v>
       </c>
       <c r="F67">
-        <v>-1.251358747437189</v>
+        <v>-2.846042120429505</v>
       </c>
       <c r="G67">
-        <v>-3.960165109474088</v>
+        <v>-8.81010108232422</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.435143993071638</v>
       </c>
       <c r="E68">
-        <v>-20.2157123339911</v>
+        <v>-25.18049575535248</v>
       </c>
       <c r="F68">
-        <v>-1.754215466001607</v>
+        <v>-2.634287969887928</v>
       </c>
       <c r="G68">
-        <v>-5.764187311280215</v>
+        <v>-7.898270903351679</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.514703541502151</v>
       </c>
       <c r="E69">
-        <v>-20.36899212220272</v>
+        <v>-26.02923593929208</v>
       </c>
       <c r="F69">
-        <v>-1.138420719342414</v>
+        <v>-3.426179728402579</v>
       </c>
       <c r="G69">
-        <v>-5.282638667683367</v>
+        <v>-7.695377498886366</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.62370337974922</v>
       </c>
       <c r="E70">
-        <v>-19.25806687864103</v>
+        <v>-26.88744063390771</v>
       </c>
       <c r="F70">
-        <v>-1.361006626492639</v>
+        <v>-3.007928539105726</v>
       </c>
       <c r="G70">
-        <v>-4.845663209227267</v>
+        <v>-7.628931539367653</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.756210651390704</v>
       </c>
       <c r="E71">
-        <v>-20.08451791351488</v>
+        <v>-26.98036492054511</v>
       </c>
       <c r="F71">
-        <v>-1.746843314965236</v>
+        <v>-2.48292606887276</v>
       </c>
       <c r="G71">
-        <v>-5.595293209503216</v>
+        <v>-10.34182760297975</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.907448013456181</v>
       </c>
       <c r="E72">
-        <v>-21.32471750457354</v>
+        <v>-25.97123977267585</v>
       </c>
       <c r="F72">
-        <v>-1.763049377597928</v>
+        <v>-3.337949096294575</v>
       </c>
       <c r="G72">
-        <v>-5.825591309942617</v>
+        <v>-9.085862904654432</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.071891006015176</v>
       </c>
       <c r="E73">
-        <v>-18.78150838796983</v>
+        <v>-25.91389117784271</v>
       </c>
       <c r="F73">
-        <v>-1.601245311629311</v>
+        <v>-2.461142985858848</v>
       </c>
       <c r="G73">
-        <v>-6.686594683250727</v>
+        <v>-8.968494133650649</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.240297623616258</v>
       </c>
       <c r="E74">
-        <v>-20.45645054071286</v>
+        <v>-26.03554410358477</v>
       </c>
       <c r="F74">
-        <v>-1.881768724137016</v>
+        <v>-2.574890287676413</v>
       </c>
       <c r="G74">
-        <v>-5.560294122062041</v>
+        <v>-9.233394056066512</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.404504687967398</v>
       </c>
       <c r="E75">
-        <v>-20.12139327735934</v>
+        <v>-26.38201764991162</v>
       </c>
       <c r="F75">
-        <v>-1.667977135935225</v>
+        <v>-4.137170245785881</v>
       </c>
       <c r="G75">
-        <v>-5.595356109868463</v>
+        <v>-8.5413774798105</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.561109220043484</v>
       </c>
       <c r="E76">
-        <v>-21.55877168365998</v>
+        <v>-28.70138429631618</v>
       </c>
       <c r="F76">
-        <v>-1.83582462367716</v>
+        <v>-3.239651637535079</v>
       </c>
       <c r="G76">
-        <v>-5.343817549249098</v>
+        <v>-8.692305250945873</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.704556573054828</v>
       </c>
       <c r="E77">
-        <v>-22.26667179748702</v>
+        <v>-28.83864687196268</v>
       </c>
       <c r="F77">
-        <v>-1.630170116468897</v>
+        <v>-3.41146947600702</v>
       </c>
       <c r="G77">
-        <v>-5.090785932591523</v>
+        <v>-9.89827409053712</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.828306558878745</v>
       </c>
       <c r="E78">
-        <v>-22.70140530222338</v>
+        <v>-26.9784720184099</v>
       </c>
       <c r="F78">
-        <v>-1.53981494287533</v>
+        <v>-3.17334503826746</v>
       </c>
       <c r="G78">
-        <v>-5.730913018065</v>
+        <v>-9.471548081070603</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.930519839867409</v>
       </c>
       <c r="E79">
-        <v>-21.98429427226473</v>
+        <v>-28.3525921712974</v>
       </c>
       <c r="F79">
-        <v>-2.520273021770653</v>
+        <v>-3.17345273026971</v>
       </c>
       <c r="G79">
-        <v>-5.912873843085501</v>
+        <v>-10.34685963219945</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.007059091174948</v>
       </c>
       <c r="E80">
-        <v>-21.92304666131099</v>
+        <v>-28.64504102271275</v>
       </c>
       <c r="F80">
-        <v>-1.643068609297194</v>
+        <v>-2.887411686352614</v>
       </c>
       <c r="G80">
-        <v>-5.860603639565949</v>
+        <v>-10.22240298319608</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.051608461668999</v>
       </c>
       <c r="E81">
-        <v>-21.90204359886341</v>
+        <v>-27.24772602595797</v>
       </c>
       <c r="F81">
-        <v>-1.681505943717867</v>
+        <v>-3.613578065670614</v>
       </c>
       <c r="G81">
-        <v>-6.05024161969202</v>
+        <v>-8.500833228591045</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.060985424681858</v>
       </c>
       <c r="E82">
-        <v>-23.29245720123051</v>
+        <v>-30.246318488773</v>
       </c>
       <c r="F82">
-        <v>-2.32525547534344</v>
+        <v>-3.873535473160422</v>
       </c>
       <c r="G82">
-        <v>-4.617460684114225</v>
+        <v>-9.58825474296653</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.030648319560249</v>
       </c>
       <c r="E83">
-        <v>-25.22865154795004</v>
+        <v>-30.05748791536416</v>
       </c>
       <c r="F83">
-        <v>-1.707795461914162</v>
+        <v>-3.839712265924382</v>
       </c>
       <c r="G83">
-        <v>-4.847914380193971</v>
+        <v>-8.780104229192883</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.955239011738817</v>
       </c>
       <c r="E84">
-        <v>-25.32527559785171</v>
+        <v>-29.09148516123294</v>
       </c>
       <c r="F84">
-        <v>-1.710814005388989</v>
+        <v>-2.558259000005426</v>
       </c>
       <c r="G84">
-        <v>-5.616202615129254</v>
+        <v>-9.81056118647413</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.830146211341845</v>
       </c>
       <c r="E85">
-        <v>-27.80703785064533</v>
+        <v>-27.90857982331933</v>
       </c>
       <c r="F85">
-        <v>-1.633869653487364</v>
+        <v>-3.294735304832936</v>
       </c>
       <c r="G85">
-        <v>-4.707666428968286</v>
+        <v>-8.26142450682757</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.651311738131247</v>
       </c>
       <c r="E86">
-        <v>-27.9789387239765</v>
+        <v>-29.81305220961513</v>
       </c>
       <c r="F86">
-        <v>-1.57232921717226</v>
+        <v>-3.180786080511153</v>
       </c>
       <c r="G86">
-        <v>-3.990191757515278</v>
+        <v>-10.36151872784734</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.414425569011347</v>
       </c>
       <c r="E87">
-        <v>-29.23943493553753</v>
+        <v>-31.87723934568746</v>
       </c>
       <c r="F87">
-        <v>-1.778570487422193</v>
+        <v>-3.746683796745553</v>
       </c>
       <c r="G87">
-        <v>-5.109050212331683</v>
+        <v>-8.790343746545849</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.115143442493631</v>
       </c>
       <c r="E88">
-        <v>-31.3126156209891</v>
+        <v>-33.8297860120487</v>
       </c>
       <c r="F88">
-        <v>-1.370417798895138</v>
+        <v>-3.43263174630208</v>
       </c>
       <c r="G88">
-        <v>-5.230838561630391</v>
+        <v>-7.530671237216545</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.750652125448894</v>
       </c>
       <c r="E89">
-        <v>-31.49741585253112</v>
+        <v>-35.35306051332683</v>
       </c>
       <c r="F89">
-        <v>-1.561782527628391</v>
+        <v>-2.690503195062366</v>
       </c>
       <c r="G89">
-        <v>-5.9271456049053</v>
+        <v>-9.49722798281873</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.318404854132263</v>
       </c>
       <c r="E90">
-        <v>-32.95627054681314</v>
+        <v>-36.44737078575438</v>
       </c>
       <c r="F90">
-        <v>-1.423446607767713</v>
+        <v>-4.160852984045362</v>
       </c>
       <c r="G90">
-        <v>-3.849672341555373</v>
+        <v>-7.349352658030663</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.819703709508722</v>
       </c>
       <c r="E91">
-        <v>-33.08166625632253</v>
+        <v>-37.04326588771271</v>
       </c>
       <c r="F91">
-        <v>-1.180244017010296</v>
+        <v>-3.060470358409302</v>
       </c>
       <c r="G91">
-        <v>-5.738355124437281</v>
+        <v>-7.537087074471652</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.2551868429394229</v>
       </c>
       <c r="E92">
-        <v>-35.8541021987205</v>
+        <v>-38.55702380086372</v>
       </c>
       <c r="F92">
-        <v>-1.222586770218443</v>
+        <v>-2.560267139106203</v>
       </c>
       <c r="G92">
-        <v>-3.661471138193345</v>
+        <v>-7.747796676955185</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.372691050185895</v>
       </c>
       <c r="E93">
-        <v>-36.58038565278169</v>
+        <v>-41.0009755599303</v>
       </c>
       <c r="F93">
-        <v>-1.332957611024291</v>
+        <v>-2.195016251975446</v>
       </c>
       <c r="G93">
-        <v>-5.113817397908233</v>
+        <v>-7.445610080130511</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.053581714583523</v>
       </c>
       <c r="E94">
-        <v>-38.62549885633371</v>
+        <v>-41.51252104078476</v>
       </c>
       <c r="F94">
-        <v>-1.621172291310328</v>
+        <v>-2.51123481211124</v>
       </c>
       <c r="G94">
-        <v>-3.647467530562228</v>
+        <v>-7.674610446718517</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.780762662774472</v>
       </c>
       <c r="E95">
-        <v>-40.39115766463539</v>
+        <v>-44.08238022692361</v>
       </c>
       <c r="F95">
-        <v>-1.292900145452124</v>
+        <v>-2.710449179214368</v>
       </c>
       <c r="G95">
-        <v>-5.277543738098429</v>
+        <v>-8.012097390628441</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.549456680479906</v>
       </c>
       <c r="E96">
-        <v>-43.95092994766595</v>
+        <v>-44.28010698752052</v>
       </c>
       <c r="F96">
-        <v>-0.9050576934376225</v>
+        <v>-2.906119212478743</v>
       </c>
       <c r="G96">
-        <v>-4.408581813313909</v>
+        <v>-7.933587803164624</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.338019173984836</v>
       </c>
       <c r="E97">
-        <v>-44.62868401002394</v>
+        <v>-47.52833384424539</v>
       </c>
       <c r="F97">
-        <v>-0.8937896258492708</v>
+        <v>-2.934442209070462</v>
       </c>
       <c r="G97">
-        <v>-4.844666735019946</v>
+        <v>-6.799394901410315</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.149174857154081</v>
       </c>
       <c r="E98">
-        <v>-46.34921883907619</v>
+        <v>-49.08044793224137</v>
       </c>
       <c r="F98">
-        <v>-1.416486220269356</v>
+        <v>-2.770934867389789</v>
       </c>
       <c r="G98">
-        <v>-6.080231851732278</v>
+        <v>-9.44208422577109</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.951175112494243</v>
       </c>
       <c r="E99">
-        <v>-50.52946904521573</v>
+        <v>-49.15934074216599</v>
       </c>
       <c r="F99">
-        <v>-1.490792909968818</v>
+        <v>-2.927176166330426</v>
       </c>
       <c r="G99">
-        <v>-4.799140112763888</v>
+        <v>-8.258978013674049</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.763182239130881</v>
       </c>
       <c r="E100">
-        <v>-51.32923151852537</v>
+        <v>-49.75477393977555</v>
       </c>
       <c r="F100">
-        <v>-1.52056262191429</v>
+        <v>-2.836524047877714</v>
       </c>
       <c r="G100">
-        <v>-5.958185279881506</v>
+        <v>-8.266675032052854</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.519188177066762</v>
       </c>
       <c r="E101">
-        <v>-52.15658032337124</v>
+        <v>-54.23018102478702</v>
       </c>
       <c r="F101">
-        <v>-1.513012303962433</v>
+        <v>-2.588221924072583</v>
       </c>
       <c r="G101">
-        <v>-6.622926271439464</v>
+        <v>-9.304051029511177</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.300066028454759</v>
       </c>
       <c r="E102">
-        <v>-55.3366740244137</v>
+        <v>-56.12250238320174</v>
       </c>
       <c r="F102">
-        <v>-1.116993970159476</v>
+        <v>-2.212813147200197</v>
       </c>
       <c r="G102">
-        <v>-5.685846561638901</v>
+        <v>-9.524672405339288</v>
       </c>
     </row>
   </sheetData>
